--- a/docs/roomly-production-readiness.xlsx
+++ b/docs/roomly-production-readiness.xlsx
@@ -949,12 +949,16 @@
       </c>
       <c r="J2" s="15" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="K2" s="15" t="inlineStr"/>
       <c r="L2" s="16" t="inlineStr"/>
-      <c r="M2" s="15" t="inlineStr"/>
+      <c r="M2" s="15" t="inlineStr">
+        <is>
+          <t>Migration 0034 applied 2026-10-10; security tests 38/38.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
